--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.28640727643096</v>
+        <v>6.059041182420032</v>
       </c>
       <c r="D2" t="n">
-        <v>37.8349189703403</v>
+        <v>6.148174332680299</v>
       </c>
       <c r="E2" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F2" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.31259964191139</v>
+        <v>5.413297441810601</v>
       </c>
       <c r="D3" t="n">
-        <v>12.97112177107285</v>
+        <v>2.107807287799337</v>
       </c>
       <c r="E3" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F3" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.81174971253235</v>
+        <v>7.606909328286508</v>
       </c>
       <c r="D4" t="n">
-        <v>27.06473720544871</v>
+        <v>4.398019795885416</v>
       </c>
       <c r="E4" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F4" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.65983724566819</v>
+        <v>2.707223552421081</v>
       </c>
       <c r="D5" t="n">
-        <v>15.43286681581901</v>
+        <v>2.507840857570589</v>
       </c>
       <c r="E5" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F5" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.78216378873479</v>
+        <v>6.789601615669404</v>
       </c>
       <c r="D6" t="n">
-        <v>30.53686296920494</v>
+        <v>4.962240232495803</v>
       </c>
       <c r="E6" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F6" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.1615035820485</v>
+        <v>7.663744332082882</v>
       </c>
       <c r="D7" t="n">
-        <v>31.30025948699213</v>
+        <v>5.086292166636222</v>
       </c>
       <c r="E7" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F7" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.60354097828652</v>
+        <v>6.273075408971559</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29543760080783</v>
+        <v>4.760508610131272</v>
       </c>
       <c r="E8" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F8" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.10254041218568</v>
+        <v>6.516662816980173</v>
       </c>
       <c r="D9" t="n">
-        <v>34.43494440796093</v>
+        <v>5.595678466293652</v>
       </c>
       <c r="E9" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F9" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.56678755283285</v>
+        <v>5.292102977335338</v>
       </c>
       <c r="D10" t="n">
-        <v>19.45085701505353</v>
+        <v>3.160764264946199</v>
       </c>
       <c r="E10" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F10" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.3940468671907</v>
+        <v>7.37653261591849</v>
       </c>
       <c r="D11" t="n">
-        <v>12.16552506059644</v>
+        <v>1.976897822346921</v>
       </c>
       <c r="E11" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F11" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.12512245228354</v>
+        <v>7.820332398496076</v>
       </c>
       <c r="D12" t="n">
-        <v>23.78818621386995</v>
+        <v>3.865580259753867</v>
       </c>
       <c r="E12" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F12" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.55490521252611</v>
+        <v>10.65267209703549</v>
       </c>
       <c r="D13" t="n">
-        <v>44.52527372178637</v>
+        <v>7.235356979790286</v>
       </c>
       <c r="E13" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F13" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>81.9466554176928</v>
+        <v>13.31633150537508</v>
       </c>
       <c r="D14" t="n">
-        <v>63.80634764660958</v>
+        <v>10.36853149257406</v>
       </c>
       <c r="E14" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F14" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.63846284534354</v>
+        <v>3.678750212368326</v>
       </c>
       <c r="D15" t="n">
-        <v>9.838981428763624</v>
+        <v>1.598834482174089</v>
       </c>
       <c r="E15" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F15" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>100.8537648626575</v>
+        <v>16.38873679018185</v>
       </c>
       <c r="D16" t="n">
-        <v>80.95366668520069</v>
+        <v>13.15497083634511</v>
       </c>
       <c r="E16" t="n">
-        <v>21.00230594568285</v>
+        <v>3.412874716173463</v>
       </c>
       <c r="F16" t="n">
-        <v>18.94265195107246</v>
+        <v>3.078180942049275</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
